--- a/backend/data/financials_by_company/0254.HK.xlsx
+++ b/backend/data/financials_by_company/0254.HK.xlsx
@@ -657,556 +657,556 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3357420</v>
+        <v>3667526.602935</v>
       </c>
       <c r="C2" t="n">
-        <v>0.165</v>
+        <v>0.04547</v>
       </c>
       <c r="D2" t="n">
-        <v>-3031000</v>
+        <v>25857000</v>
       </c>
       <c r="E2" t="n">
-        <v>20348000</v>
+        <v>80658000</v>
       </c>
       <c r="F2" t="n">
-        <v>20348000</v>
+        <v>80658000</v>
       </c>
       <c r="G2" t="n">
-        <v>-8629000</v>
+        <v>54756000</v>
       </c>
       <c r="H2" t="n">
-        <v>18509000</v>
+        <v>24437000</v>
       </c>
       <c r="I2" t="n">
-        <v>78427000</v>
+        <v>105886000</v>
       </c>
       <c r="J2" t="n">
-        <v>17317000</v>
+        <v>106515000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1192000</v>
+        <v>82078000</v>
       </c>
       <c r="L2" t="n">
-        <v>-4818000</v>
+        <v>-20689000</v>
       </c>
       <c r="M2" t="n">
-        <v>6853000</v>
+        <v>20675000</v>
       </c>
       <c r="N2" t="n">
-        <v>2064000</v>
+        <v>8000</v>
       </c>
       <c r="O2" t="n">
-        <v>-25619580</v>
+        <v>-22234473.397065</v>
       </c>
       <c r="P2" t="n">
-        <v>-8629000</v>
+        <v>54756000</v>
       </c>
       <c r="Q2" t="n">
-        <v>110861000</v>
+        <v>141767000</v>
       </c>
       <c r="R2" t="n">
-        <v>-435000</v>
+        <v>82100000</v>
       </c>
       <c r="S2" t="n">
-        <v>408161748</v>
+        <v>119015861</v>
       </c>
       <c r="T2" t="n">
-        <v>4081617480</v>
+        <v>119015861</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.021</v>
+        <v>0.854</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.021</v>
+        <v>0.854</v>
       </c>
       <c r="W2" t="n">
-        <v>-8629000</v>
+        <v>54756000</v>
       </c>
       <c r="X2" t="n">
-        <v>-8629000</v>
+        <v>54756000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-8629000</v>
+        <v>54756000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1594000</v>
+        <v>-3855000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-10223000</v>
+        <v>58611000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-10223000</v>
+        <v>58611000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2178000</v>
+        <v>2792000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-8045000</v>
+        <v>61403000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-169000</v>
+        <v>387000</v>
       </c>
       <c r="AG2" t="n">
-        <v>20348000</v>
+        <v>80658000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1414000</v>
+        <v>-85786000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-18934000</v>
+        <v>5128000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-4818000</v>
+        <v>-20689000</v>
       </c>
       <c r="AK2" t="n">
-        <v>29000</v>
+        <v>22000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6853000</v>
+        <v>20675000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2064000</v>
+        <v>8000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-26123000</v>
+        <v>1047000</v>
       </c>
       <c r="AO2" t="n">
-        <v>32434000</v>
+        <v>35881000</v>
       </c>
       <c r="AP2" t="n">
-        <v>32434000</v>
+        <v>35881000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>32434000</v>
+        <v>35881000</v>
       </c>
       <c r="AR2" t="n">
-        <v>6311000</v>
+        <v>36928000</v>
       </c>
       <c r="AS2" t="n">
-        <v>78427000</v>
+        <v>105886000</v>
       </c>
       <c r="AT2" t="n">
-        <v>84738000</v>
+        <v>142814000</v>
       </c>
       <c r="AU2" t="n">
-        <v>84738000</v>
+        <v>142814000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2647326.991006</v>
+        <v>58455045</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009683000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="D3" t="n">
-        <v>-121144000</v>
+        <v>-55275000</v>
       </c>
       <c r="E3" t="n">
-        <v>297331000</v>
+        <v>354273000</v>
       </c>
       <c r="F3" t="n">
-        <v>273411000</v>
+        <v>354273000</v>
       </c>
       <c r="G3" t="n">
-        <v>178946000</v>
+        <v>300283000</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>183804000</v>
+        <v>86230000</v>
       </c>
       <c r="J3" t="n">
-        <v>176187000</v>
+        <v>298998000</v>
       </c>
       <c r="K3" t="n">
-        <v>176187000</v>
+        <v>298998000</v>
       </c>
       <c r="L3" t="n">
-        <v>-14129000</v>
+        <v>-10935000</v>
       </c>
       <c r="M3" t="n">
-        <v>16519000</v>
+        <v>11268000</v>
       </c>
       <c r="N3" t="n">
-        <v>2418000</v>
+        <v>335000</v>
       </c>
       <c r="O3" t="n">
-        <v>-91817673.008994</v>
+        <v>4465045</v>
       </c>
       <c r="P3" t="n">
-        <v>178946000</v>
+        <v>300283000</v>
       </c>
       <c r="Q3" t="n">
-        <v>250470000</v>
+        <v>135668000</v>
       </c>
       <c r="R3" t="n">
-        <v>138756000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+        <v>299000000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>272063596</v>
+      </c>
+      <c r="T3" t="n">
+        <v>272063596</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.104</v>
+      </c>
       <c r="W3" t="n">
-        <v>178946000</v>
+        <v>300283000</v>
       </c>
       <c r="X3" t="n">
-        <v>178946000</v>
+        <v>300283000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>178946000</v>
+        <v>300283000</v>
       </c>
       <c r="AA3" t="n">
-        <v>20824000</v>
+        <v>7591000</v>
       </c>
       <c r="AB3" t="n">
-        <v>158122000</v>
+        <v>292692000</v>
       </c>
       <c r="AC3" t="n">
-        <v>158122000</v>
+        <v>292692000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1546000</v>
+        <v>-4962000</v>
       </c>
       <c r="AE3" t="n">
-        <v>159668000</v>
+        <v>287730000</v>
       </c>
       <c r="AF3" t="n">
-        <v>709000</v>
+        <v>2986000</v>
       </c>
       <c r="AG3" t="n">
-        <v>273411000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>354273000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-354273000</v>
+      </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-14129000</v>
+        <v>-10935000</v>
       </c>
       <c r="AK3" t="n">
-        <v>28000</v>
+        <v>2000</v>
       </c>
       <c r="AL3" t="n">
-        <v>16519000</v>
+        <v>11268000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2418000</v>
+        <v>335000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-100122000</v>
+        <v>-58594000</v>
       </c>
       <c r="AO3" t="n">
-        <v>66666000</v>
+        <v>49438000</v>
       </c>
       <c r="AP3" t="n">
-        <v>66666000</v>
+        <v>49438000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>66666000</v>
+        <v>49438000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-33456000</v>
+        <v>-9156000</v>
       </c>
       <c r="AS3" t="n">
-        <v>183804000</v>
+        <v>86230000</v>
       </c>
       <c r="AT3" t="n">
-        <v>150348000</v>
+        <v>77074000</v>
       </c>
       <c r="AU3" t="n">
-        <v>150348000</v>
+        <v>77074000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>58455045</v>
+        <v>2647326.991006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.165</v>
+        <v>0.009683000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>-55275000</v>
+        <v>-121144000</v>
       </c>
       <c r="E4" t="n">
-        <v>354273000</v>
+        <v>297331000</v>
       </c>
       <c r="F4" t="n">
-        <v>354273000</v>
+        <v>273411000</v>
       </c>
       <c r="G4" t="n">
-        <v>300283000</v>
+        <v>178946000</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>86230000</v>
+        <v>183804000</v>
       </c>
       <c r="J4" t="n">
-        <v>298998000</v>
+        <v>176187000</v>
       </c>
       <c r="K4" t="n">
-        <v>298998000</v>
+        <v>176187000</v>
       </c>
       <c r="L4" t="n">
-        <v>-10935000</v>
+        <v>-14129000</v>
       </c>
       <c r="M4" t="n">
-        <v>11268000</v>
+        <v>16519000</v>
       </c>
       <c r="N4" t="n">
-        <v>335000</v>
+        <v>2418000</v>
       </c>
       <c r="O4" t="n">
-        <v>4465045</v>
+        <v>-91817673.008994</v>
       </c>
       <c r="P4" t="n">
-        <v>300283000</v>
+        <v>178946000</v>
       </c>
       <c r="Q4" t="n">
-        <v>135668000</v>
+        <v>250470000</v>
       </c>
       <c r="R4" t="n">
-        <v>299000000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>272063596</v>
-      </c>
-      <c r="T4" t="n">
-        <v>272063596</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.104</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.104</v>
-      </c>
+        <v>138756000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>300283000</v>
+        <v>178946000</v>
       </c>
       <c r="X4" t="n">
-        <v>300283000</v>
+        <v>178946000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>300283000</v>
+        <v>178946000</v>
       </c>
       <c r="AA4" t="n">
-        <v>7591000</v>
+        <v>20824000</v>
       </c>
       <c r="AB4" t="n">
-        <v>292692000</v>
+        <v>158122000</v>
       </c>
       <c r="AC4" t="n">
-        <v>292692000</v>
+        <v>158122000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-4962000</v>
+        <v>1546000</v>
       </c>
       <c r="AE4" t="n">
-        <v>287730000</v>
+        <v>159668000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2986000</v>
+        <v>709000</v>
       </c>
       <c r="AG4" t="n">
-        <v>354273000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-354273000</v>
-      </c>
+        <v>273411000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-10935000</v>
+        <v>-14129000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2000</v>
+        <v>28000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11268000</v>
+        <v>16519000</v>
       </c>
       <c r="AM4" t="n">
-        <v>335000</v>
+        <v>2418000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-58594000</v>
+        <v>-100122000</v>
       </c>
       <c r="AO4" t="n">
-        <v>49438000</v>
+        <v>66666000</v>
       </c>
       <c r="AP4" t="n">
-        <v>49438000</v>
+        <v>66666000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>49438000</v>
+        <v>66666000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-9156000</v>
+        <v>-33456000</v>
       </c>
       <c r="AS4" t="n">
-        <v>86230000</v>
+        <v>183804000</v>
       </c>
       <c r="AT4" t="n">
-        <v>77074000</v>
+        <v>150348000</v>
       </c>
       <c r="AU4" t="n">
-        <v>77074000</v>
+        <v>150348000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>3667526.602935</v>
+        <v>3357420</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04547</v>
+        <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>25857000</v>
+        <v>-3031000</v>
       </c>
       <c r="E5" t="n">
-        <v>80658000</v>
+        <v>20348000</v>
       </c>
       <c r="F5" t="n">
-        <v>80658000</v>
+        <v>20348000</v>
       </c>
       <c r="G5" t="n">
-        <v>54756000</v>
+        <v>-8629000</v>
       </c>
       <c r="H5" t="n">
-        <v>24437000</v>
+        <v>18509000</v>
       </c>
       <c r="I5" t="n">
-        <v>105886000</v>
+        <v>78427000</v>
       </c>
       <c r="J5" t="n">
-        <v>106515000</v>
+        <v>17317000</v>
       </c>
       <c r="K5" t="n">
-        <v>82078000</v>
+        <v>-1192000</v>
       </c>
       <c r="L5" t="n">
-        <v>-20689000</v>
+        <v>-4818000</v>
       </c>
       <c r="M5" t="n">
-        <v>20675000</v>
+        <v>6853000</v>
       </c>
       <c r="N5" t="n">
-        <v>8000</v>
+        <v>2064000</v>
       </c>
       <c r="O5" t="n">
-        <v>-22234473.397065</v>
+        <v>-25619580</v>
       </c>
       <c r="P5" t="n">
-        <v>54756000</v>
+        <v>-8629000</v>
       </c>
       <c r="Q5" t="n">
-        <v>141767000</v>
+        <v>110861000</v>
       </c>
       <c r="R5" t="n">
-        <v>82100000</v>
+        <v>-435000</v>
       </c>
       <c r="S5" t="n">
-        <v>119015861</v>
+        <v>408161748</v>
       </c>
       <c r="T5" t="n">
-        <v>119015861</v>
+        <v>4081617480</v>
       </c>
       <c r="U5" t="n">
-        <v>0.854</v>
+        <v>-0.021</v>
       </c>
       <c r="V5" t="n">
-        <v>0.854</v>
+        <v>-0.021</v>
       </c>
       <c r="W5" t="n">
-        <v>54756000</v>
+        <v>-8629000</v>
       </c>
       <c r="X5" t="n">
-        <v>54756000</v>
+        <v>-8629000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>54756000</v>
+        <v>-8629000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3855000</v>
+        <v>1594000</v>
       </c>
       <c r="AB5" t="n">
-        <v>58611000</v>
+        <v>-10223000</v>
       </c>
       <c r="AC5" t="n">
-        <v>58611000</v>
+        <v>-10223000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2792000</v>
+        <v>2178000</v>
       </c>
       <c r="AE5" t="n">
-        <v>61403000</v>
+        <v>-8045000</v>
       </c>
       <c r="AF5" t="n">
-        <v>387000</v>
+        <v>-169000</v>
       </c>
       <c r="AG5" t="n">
-        <v>80658000</v>
+        <v>20348000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-85786000</v>
+        <v>-1414000</v>
       </c>
       <c r="AI5" t="n">
-        <v>5128000</v>
+        <v>-18934000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-20689000</v>
+        <v>-4818000</v>
       </c>
       <c r="AK5" t="n">
-        <v>22000</v>
+        <v>29000</v>
       </c>
       <c r="AL5" t="n">
-        <v>20675000</v>
+        <v>6853000</v>
       </c>
       <c r="AM5" t="n">
-        <v>8000</v>
+        <v>2064000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1047000</v>
+        <v>-26123000</v>
       </c>
       <c r="AO5" t="n">
-        <v>35881000</v>
+        <v>32434000</v>
       </c>
       <c r="AP5" t="n">
-        <v>35881000</v>
+        <v>32434000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>35881000</v>
+        <v>32434000</v>
       </c>
       <c r="AR5" t="n">
-        <v>36928000</v>
+        <v>6311000</v>
       </c>
       <c r="AS5" t="n">
-        <v>105886000</v>
+        <v>78427000</v>
       </c>
       <c r="AT5" t="n">
-        <v>142814000</v>
+        <v>84738000</v>
       </c>
       <c r="AU5" t="n">
-        <v>142814000</v>
+        <v>84738000</v>
       </c>
     </row>
   </sheetData>
@@ -1502,105 +1502,107 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>438762840</v>
+        <v>119015861</v>
       </c>
       <c r="C2" t="n">
-        <v>438762840</v>
+        <v>119015861</v>
       </c>
       <c r="D2" t="n">
-        <v>23176000</v>
+        <v>422668000</v>
       </c>
       <c r="E2" t="n">
-        <v>216044000</v>
+        <v>587881000</v>
       </c>
       <c r="F2" t="n">
-        <v>88818000</v>
+        <v>-484815000</v>
       </c>
       <c r="G2" t="n">
-        <v>212171000</v>
+        <v>-22342000</v>
       </c>
       <c r="H2" t="n">
-        <v>-147347000</v>
+        <v>-696202000</v>
       </c>
       <c r="I2" t="n">
-        <v>88818000</v>
+        <v>-484815000</v>
       </c>
       <c r="J2" t="n">
-        <v>147110000</v>
+        <v>163077000</v>
       </c>
       <c r="K2" t="n">
-        <v>143237000</v>
+        <v>-447146000</v>
       </c>
       <c r="L2" t="n">
-        <v>143237000</v>
+        <v>-447146000</v>
       </c>
       <c r="M2" t="n">
-        <v>103249000</v>
+        <v>-470447000</v>
       </c>
       <c r="N2" t="n">
-        <v>-39988000</v>
+        <v>-23301000</v>
       </c>
       <c r="O2" t="n">
-        <v>143237000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>-447146000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>62077000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-3694404000</v>
+      </c>
       <c r="R2" t="n">
-        <v>3587769000</v>
+        <v>3178754000</v>
       </c>
       <c r="S2" t="n">
-        <v>3587769000</v>
+        <v>3178754000</v>
       </c>
       <c r="T2" t="n">
-        <v>368834000</v>
+        <v>784987000</v>
       </c>
       <c r="U2" t="n">
-        <v>4045000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3767000</v>
-      </c>
+        <v>1663000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>278000</v>
+        <v>1663000</v>
       </c>
       <c r="X2" t="n">
-        <v>278000</v>
+        <v>1663000</v>
       </c>
       <c r="Y2" t="n">
-        <v>364789000</v>
+        <v>783324000</v>
       </c>
       <c r="Z2" t="n">
-        <v>215766000</v>
+        <v>586218000</v>
       </c>
       <c r="AA2" t="n">
-        <v>146832000</v>
+        <v>161414000</v>
       </c>
       <c r="AB2" t="n">
-        <v>68934000</v>
+        <v>424804000</v>
       </c>
       <c r="AC2" t="n">
-        <v>86925000</v>
+        <v>158429000</v>
       </c>
       <c r="AD2" t="n">
-        <v>77365000</v>
+        <v>151206000</v>
       </c>
       <c r="AE2" t="n">
-        <v>9560000</v>
+        <v>7223000</v>
       </c>
       <c r="AF2" t="n">
-        <v>472083000</v>
+        <v>314540000</v>
       </c>
       <c r="AG2" t="n">
-        <v>254641000</v>
+        <v>227418000</v>
       </c>
       <c r="AH2" t="n">
-        <v>31539000</v>
+        <v>14694000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5380000</v>
+        <v>7046000</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -1609,57 +1611,61 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>54419000</v>
+        <v>37669000</v>
       </c>
       <c r="AM2" t="n">
-        <v>27931000</v>
+        <v>123000</v>
       </c>
       <c r="AN2" t="n">
-        <v>26488000</v>
+        <v>37546000</v>
       </c>
       <c r="AO2" t="n">
-        <v>163303000</v>
+        <v>168009000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-103167000</v>
+        <v>-57430000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>266470000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>225439000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>168009000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>248057000</v>
+        <v>222187000</v>
       </c>
       <c r="AT2" t="n">
-        <v>18413000</v>
+        <v>3252000</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>217442000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>87122000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>21992000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>93577000</v>
+        <v>25076000</v>
       </c>
       <c r="AY2" t="n">
-        <v>78107000</v>
+        <v>59910000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-10822000</v>
+        <v>-5582000</v>
       </c>
       <c r="BA2" t="n">
-        <v>88929000</v>
+        <v>65492000</v>
       </c>
       <c r="BB2" t="n">
-        <v>45758000</v>
+        <v>2136000</v>
       </c>
       <c r="BC2" t="n">
-        <v>45758000</v>
+        <v>2136000</v>
       </c>
       <c r="BD2" t="n">
-        <v>45758000</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="3">
@@ -1814,107 +1820,105 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>119015861</v>
+        <v>438762840</v>
       </c>
       <c r="C4" t="n">
-        <v>119015861</v>
+        <v>438762840</v>
       </c>
       <c r="D4" t="n">
-        <v>422668000</v>
+        <v>23176000</v>
       </c>
       <c r="E4" t="n">
-        <v>587881000</v>
+        <v>216044000</v>
       </c>
       <c r="F4" t="n">
-        <v>-484815000</v>
+        <v>88818000</v>
       </c>
       <c r="G4" t="n">
-        <v>-22342000</v>
+        <v>212171000</v>
       </c>
       <c r="H4" t="n">
-        <v>-696202000</v>
+        <v>-147347000</v>
       </c>
       <c r="I4" t="n">
-        <v>-484815000</v>
+        <v>88818000</v>
       </c>
       <c r="J4" t="n">
-        <v>163077000</v>
+        <v>147110000</v>
       </c>
       <c r="K4" t="n">
-        <v>-447146000</v>
+        <v>143237000</v>
       </c>
       <c r="L4" t="n">
-        <v>-447146000</v>
+        <v>143237000</v>
       </c>
       <c r="M4" t="n">
-        <v>-470447000</v>
+        <v>103249000</v>
       </c>
       <c r="N4" t="n">
-        <v>-23301000</v>
+        <v>-39988000</v>
       </c>
       <c r="O4" t="n">
-        <v>-447146000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>62077000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-3694404000</v>
-      </c>
+        <v>143237000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>3178754000</v>
+        <v>3587769000</v>
       </c>
       <c r="S4" t="n">
-        <v>3178754000</v>
+        <v>3587769000</v>
       </c>
       <c r="T4" t="n">
-        <v>784987000</v>
+        <v>368834000</v>
       </c>
       <c r="U4" t="n">
-        <v>1663000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>4045000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3767000</v>
+      </c>
       <c r="W4" t="n">
-        <v>1663000</v>
+        <v>278000</v>
       </c>
       <c r="X4" t="n">
-        <v>1663000</v>
+        <v>278000</v>
       </c>
       <c r="Y4" t="n">
-        <v>783324000</v>
+        <v>364789000</v>
       </c>
       <c r="Z4" t="n">
-        <v>586218000</v>
+        <v>215766000</v>
       </c>
       <c r="AA4" t="n">
-        <v>161414000</v>
+        <v>146832000</v>
       </c>
       <c r="AB4" t="n">
-        <v>424804000</v>
+        <v>68934000</v>
       </c>
       <c r="AC4" t="n">
-        <v>158429000</v>
+        <v>86925000</v>
       </c>
       <c r="AD4" t="n">
-        <v>151206000</v>
+        <v>77365000</v>
       </c>
       <c r="AE4" t="n">
-        <v>7223000</v>
+        <v>9560000</v>
       </c>
       <c r="AF4" t="n">
-        <v>314540000</v>
+        <v>472083000</v>
       </c>
       <c r="AG4" t="n">
-        <v>227418000</v>
+        <v>254641000</v>
       </c>
       <c r="AH4" t="n">
-        <v>14694000</v>
+        <v>31539000</v>
       </c>
       <c r="AI4" t="n">
-        <v>7046000</v>
+        <v>5380000</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1923,61 +1927,57 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>37669000</v>
+        <v>54419000</v>
       </c>
       <c r="AM4" t="n">
-        <v>123000</v>
+        <v>27931000</v>
       </c>
       <c r="AN4" t="n">
-        <v>37546000</v>
+        <v>26488000</v>
       </c>
       <c r="AO4" t="n">
-        <v>168009000</v>
+        <v>163303000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-57430000</v>
+        <v>-103167000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>225439000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>168009000</v>
-      </c>
+        <v>266470000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>222187000</v>
+        <v>248057000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3252000</v>
+        <v>18413000</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>87122000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>21992000</v>
-      </c>
+        <v>217442000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>25076000</v>
+        <v>93577000</v>
       </c>
       <c r="AY4" t="n">
-        <v>59910000</v>
+        <v>78107000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-5582000</v>
+        <v>-10822000</v>
       </c>
       <c r="BA4" t="n">
-        <v>65492000</v>
+        <v>88929000</v>
       </c>
       <c r="BB4" t="n">
-        <v>2136000</v>
+        <v>45758000</v>
       </c>
       <c r="BC4" t="n">
-        <v>2136000</v>
+        <v>45758000</v>
       </c>
       <c r="BD4" t="n">
-        <v>2136000</v>
+        <v>45758000</v>
       </c>
     </row>
   </sheetData>
@@ -2208,131 +2208,123 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-146247000</v>
+        <v>12248000</v>
       </c>
       <c r="C2" t="n">
-        <v>-116125000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>129372000</v>
-      </c>
+        <v>-12560000</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>80400000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-34560000</v>
+        <v>-855000</v>
       </c>
       <c r="G2" t="n">
-        <v>45758000</v>
+        <v>2136000</v>
       </c>
       <c r="H2" t="n">
-        <v>135575000</v>
+        <v>4567000</v>
       </c>
       <c r="I2" t="n">
-        <v>6743000</v>
+        <v>1651000</v>
       </c>
       <c r="J2" t="n">
-        <v>-96560000</v>
+        <v>-4082000</v>
       </c>
       <c r="K2" t="n">
-        <v>93067000</v>
+        <v>-16338000</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>80400000</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>80400000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>13247000</v>
+        <v>-12560000</v>
       </c>
       <c r="P2" t="n">
-        <v>13247000</v>
+        <v>-12560000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-116125000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>129372000</v>
-      </c>
+        <v>-12560000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
+        <v>-12560000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-12560000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-847000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-77940000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2064000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-49314000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-49314000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-30690000</v>
+        <v>-855000</v>
       </c>
       <c r="AA2" t="n">
-        <v>3870000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-34560000</v>
+        <v>-855000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-111687000</v>
+        <v>13103000</v>
       </c>
       <c r="AD2" t="n">
+        <v>-902000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-11844000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>12599000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-14641000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-9802000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-65119000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>24437000</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="n">
-        <v>-104603000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-46262000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-53106000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-5235000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4789000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>18509000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3352000</v>
-      </c>
       <c r="AL2" t="n">
-        <v>15157000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>728000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-2717000</v>
-      </c>
+        <v>24437000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-1414000</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-8045000</v>
+        <v>61403000</v>
       </c>
     </row>
     <row r="3">
@@ -2428,123 +2420,131 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>12248000</v>
+        <v>-146247000</v>
       </c>
       <c r="C4" t="n">
-        <v>-12560000</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>-116125000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>129372000</v>
+      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>80400000</v>
       </c>
       <c r="F4" t="n">
-        <v>-855000</v>
+        <v>-34560000</v>
       </c>
       <c r="G4" t="n">
-        <v>2136000</v>
+        <v>45758000</v>
       </c>
       <c r="H4" t="n">
-        <v>4567000</v>
+        <v>135575000</v>
       </c>
       <c r="I4" t="n">
-        <v>1651000</v>
+        <v>6743000</v>
       </c>
       <c r="J4" t="n">
-        <v>-4082000</v>
+        <v>-96560000</v>
       </c>
       <c r="K4" t="n">
-        <v>-16338000</v>
+        <v>93067000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
+        <v>80400000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>80400000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13247000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>13247000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-116125000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>129372000</v>
+      </c>
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>-12560000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-12560000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-12560000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>-12560000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-12560000</v>
-      </c>
       <c r="U4" t="n">
-        <v>-847000</v>
+        <v>-77940000</v>
       </c>
       <c r="V4" t="n">
-        <v>8000</v>
+        <v>2064000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-49314000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>-49314000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-30690000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3870000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-34560000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-111687000</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>-855000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-855000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>13103000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-902000</v>
-      </c>
       <c r="AE4" t="n">
-        <v>-11844000</v>
+        <v>-104603000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12599000</v>
+        <v>-46262000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-14641000</v>
+        <v>-53106000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-9802000</v>
+        <v>-5235000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-65119000</v>
+        <v>4789000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24437000</v>
+        <v>18509000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3352000</v>
       </c>
       <c r="AL4" t="n">
-        <v>24437000</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+        <v>15157000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>728000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-2717000</v>
+      </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>-1414000</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>61403000</v>
+        <v>-8045000</v>
       </c>
     </row>
   </sheetData>
@@ -3049,187 +3049,187 @@
       </c>
       <c r="CT1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
@@ -3322,67 +3322,67 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.134</v>
+        <v>0.215</v>
       </c>
       <c r="AC2" t="n">
-        <v>740530</v>
+        <v>98828358</v>
       </c>
       <c r="AD2" t="n">
-        <v>740530</v>
+        <v>98828358</v>
       </c>
       <c r="AE2" t="n">
-        <v>1468585</v>
+        <v>6912150</v>
       </c>
       <c r="AF2" t="n">
-        <v>5059050</v>
+        <v>31903010</v>
       </c>
       <c r="AG2" t="n">
-        <v>5059050</v>
+        <v>31903010</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ2" t="n">
-        <v>558125184</v>
+        <v>750096704</v>
       </c>
       <c r="AK2" t="n">
-        <v>563762840</v>
+        <v>743339124</v>
       </c>
       <c r="AL2" t="n">
         <v>0.26</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AN2" t="n">
         <v>472.8872</v>
@@ -3391,13 +3391,13 @@
         <v>0.24</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.798528</v>
+        <v>9.136934999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7076</v>
+        <v>0.7904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.529725</v>
+        <v>0.572975</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -3414,31 +3414,31 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>637150208</v>
+        <v>704801728</v>
       </c>
       <c r="AX2" t="n">
         <v>-0.78393</v>
       </c>
       <c r="AY2" t="n">
-        <v>239965653</v>
+        <v>291764183</v>
       </c>
       <c r="AZ2" t="n">
-        <v>563762840</v>
+        <v>675762840</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.65473</v>
+        <v>0.54947</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.0000005e-05</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="BC2" t="n">
-        <v>563762840</v>
+        <v>675762840</v>
       </c>
       <c r="BD2" t="n">
         <v>0.211</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.691943</v>
+        <v>5.2606635</v>
       </c>
       <c r="BF2" t="n">
         <v>1751241600</v>
@@ -3464,16 +3464,16 @@
         <v>1755216000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.761</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>-222.702</v>
+        <v>-246.348</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.3809524</v>
+        <v>1.6829269</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="BR2" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -3580,140 +3580,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CT2" t="b">
+      <c r="CT2" t="n">
+        <v>0.90909004</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.00999999</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>1.07 - 1.14</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>6912150</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>3.269231</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>0.26 - 1.2</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.09000002999999999</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.075000025</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>168.2927</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1740491316</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1740491316</v>
+      </c>
+      <c r="DH2" t="b">
         <v>0</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="DI2" t="n">
         <v>-0.14</v>
       </c>
-      <c r="CV2" t="n">
-        <v>0.2824</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.39909557</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.460275</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0.8688941999999999</v>
-      </c>
-      <c r="CZ2" t="n">
+      <c r="DJ2" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.4043522</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.53702503</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.9372574</v>
+      </c>
+      <c r="DN2" t="n">
         <v>15</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DO2" t="n">
         <v>15</v>
       </c>
-      <c r="DB2" t="b">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>NUR HOLDINGS</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>National United Resources Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>NUR HOLDINGS</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>National United Resources Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1191547800000</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DF2" t="n">
-        <v>1780385054</v>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DW2" t="n">
+        <v>1782115692</v>
+      </c>
+      <c r="DX2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>finmb_4481694</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="EB2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="ED2" t="b">
         <v>0</v>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1191547800000</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.00999999</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.94 - 1.0</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>1468585</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>2.8076925</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>0.26 - 1.14</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.14999998</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.13157892</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>138.09523</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1740491316</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1740491316</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.99999905</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
       </c>
       <c r="EE2" t="inlineStr"/>
     </row>
